--- a/output/cards.xlsx
+++ b/output/cards.xlsx
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Meowth ex #121 Pokemon Perfect Order</t>
+          <t>Meowth ex</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cubone #407 Pokemon Chinese Gem Pack 3</t>
+          <t>Cubone</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Chansey #187 Pokemon Twilight Masquerade</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fuecoco #201 Pokemon Paldea Evolved</t>
+          <t>Fuecoco</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cleffa #202 Pokemon Obsidian Flames</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Slowpoke #204 Pokemon Scarlet &amp;amp; Violet</t>
+          <t>Slowpoke</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Hisuian Growlithe #181 Pokemon Twilight Masquerade</t>
+          <t>Hisuian Growlithe</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Machoke #177 Pokemon Scarlet &amp;amp; Violet 151</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Swablu #213 Pokemon Paradox Rift</t>
+          <t>Swablu</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Pidgey #207 Pokemon Obsidian Flames</t>
+          <t>Pidgey</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Garbodor #204 Pokemon Paradox Rift</t>
+          <t>Garbodor</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Trubbish #140 Pokemon White Flare</t>
+          <t>Trubbish</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Altaria #GG19 Pokemon Crown Zenith</t>
+          <t>Altaria</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Snorunt #188 Pokemon Paradox Rift</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Vanillish #190 Pokemon Paradox Rift</t>
+          <t>Vanillish</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Swablu #GG27 Pokemon Crown Zenith</t>
+          <t>Swablu</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Shuckle #136 Pokemon Mega Evolution</t>
+          <t>Shuckle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Penny #239 Pokemon Paldean Fates</t>
+          <t>Penny</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Penny #252 Pokemon Scarlet &amp;amp; Violet</t>
+          <t>Penny</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Penny #239 Pokemon Scarlet &amp;amp; Violet</t>
+          <t>Penny</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">

--- a/output/cards.xlsx
+++ b/output/cards.xlsx
@@ -29,10 +29,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00FBF6E8"/>
     </font>
     <font>
-      <color rgb="001F4E78"/>
+      <color rgb="00386C2C"/>
       <u val="single"/>
     </font>
     <font>
@@ -40,7 +40,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00386C2C"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -53,7 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
+        <fgColor rgb="002D5A28"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,7 +164,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="914400" cy="228600"/>
+    <ext cx="733425" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -297,6 +297,231 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="914400" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -599,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -716,32 +941,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Blastoise | Base | 2/102</t>
+          <t>top:9 Eeveelution</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Blastoise</t>
+          <t>Umbreon VMAX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Evolving Skies</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Sword &amp; Shield</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Rare Holo</t>
+          <t>Rare Rainbow</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -755,19 +980,19 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>229.23</v>
+        <v>2261.15</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>183.38</v>
+        <v>1808.92</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>194.85</v>
+        <v>1921.98</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>206.31</v>
+        <v>2035.04</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>217.77</v>
+        <v>2148.09</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -776,7 +1001,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>https://prices.pokemontcg.io/tcgplayer/base1-2</t>
+          <t>https://prices.pokemontcg.io/tcgplayer/swsh7-215</t>
         </is>
       </c>
     </row>
@@ -788,32 +1013,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charizard | Base | 4/102</t>
+          <t>top:9 Eeveelution</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Charizard</t>
+          <t>Flareon ★</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Power Keepers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rare Holo</t>
+          <t>Rare Holo Star</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,19 +1052,19 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>556.84</v>
+        <v>1999.95</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>445.47</v>
+        <v>1599.96</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>473.31</v>
+        <v>1699.96</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>501.16</v>
+        <v>1799.95</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>529</v>
+        <v>1899.95</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,7 +1073,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>https://prices.pokemontcg.io/tcgplayer/base1-4</t>
+          <t>https://prices.pokemontcg.io/tcgplayer/ex16-100</t>
         </is>
       </c>
     </row>
@@ -860,32 +1085,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mewtwo | Base | 10/102</t>
+          <t>top:9 Eeveelution</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mewtwo</t>
+          <t>Jolteon ★</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Power Keepers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rare Holo</t>
+          <t>Rare Holo Star</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -899,19 +1124,19 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>78.36</v>
+        <v>1999.94</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>62.69</v>
+        <v>1599.95</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>66.61</v>
+        <v>1699.95</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>70.52</v>
+        <v>1799.95</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>74.44</v>
+        <v>1899.94</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,7 +1145,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>https://prices.pokemontcg.io/tcgplayer/base1-10</t>
+          <t>https://prices.pokemontcg.io/tcgplayer/ex16-101</t>
         </is>
       </c>
     </row>
@@ -932,37 +1157,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pikachu | Base | 58/102</t>
+          <t>top:9 Eeveelution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Vaporeon ★</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Power Keepers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare Holo Star</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>holofoil</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -971,19 +1196,19 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6.89</v>
+        <v>900.99</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5.51</v>
+        <v>720.79</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5.86</v>
+        <v>765.84</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.2</v>
+        <v>810.89</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>6.55</v>
+        <v>855.9400000000001</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -992,7 +1217,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>https://prices.pokemontcg.io/tcgplayer/base1-58</t>
+          <t>https://prices.pokemontcg.io/tcgplayer/ex16-102</t>
         </is>
       </c>
     </row>
@@ -1004,99 +1229,747 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charizard V | Champion's Path | 74/73</t>
+          <t>top:9 Eeveelution</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Charizard V</t>
+          <t>Espeon ★</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Champion's Path</t>
+          <t>POP Series 5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1615</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1710</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/pop5-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="104.52" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>top:9 Eeveelution</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Umbreon ex</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prismatic Evolutions</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Scarlet &amp; Violet</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1557.92</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1246.34</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1324.23</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1402.13</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1480.02</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/sv8pt5-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="104.52" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>top:9 Eeveelution</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Umbreon</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aquapolis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>E-Card</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rare Holo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1252.62</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1002.1</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1064.73</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1127.36</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1189.99</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/ecard2-H29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="104.52" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>top:9 Eeveelution</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Umbreon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Skyridge</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E-Card</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rare Holo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>659.99</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>527.99</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>560.99</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>593.99</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>626.99</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/ecard3-H30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="104.52" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>top:9 Eeveelution</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gardevoir &amp; Sylveon-GX</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Unbroken Bonds</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sun &amp; Moon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rare Ultra</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>592.73</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>474.18</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>503.82</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>533.46</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>563.09</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/sm10-205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104.52" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>top:5 Charizard &lt;$50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Charizard ex</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Obsidian Flames</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Scarlet &amp; Violet</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/sv3-228</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="104.52" customHeight="1">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>top:5 Charizard &lt;$50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reshiram &amp; Charizard-GX</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SM Black Star Promos</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sun &amp; Moon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SM247</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Promo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/smp-SM247</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="104.52" customHeight="1">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>top:5 Charizard &lt;$50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Charizard ex</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Scarlet &amp; Violet</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/sv3pt5-183</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="104.52" customHeight="1">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>top:5 Charizard &lt;$50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Charizard</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Boundaries Crossed</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Black &amp; White</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Rare Holo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>holofoil</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>pokemontcg.io</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>tcgplayer</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/bw7-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="104.52" customHeight="1">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sample_cards</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>top:5 Charizard &lt;$50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Charizard VMAX</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SWSH Black Star Promos</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Sword &amp; Shield</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Rare Secret</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SWSH261</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Promo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>holofoil</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>pokemontcg.io</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>268.29</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>214.63</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>228.05</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>241.46</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>254.88</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>tcgplayer</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>https://prices.pokemontcg.io/tcgplayer/swsh35-79</t>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://prices.pokemontcg.io/tcgplayer/swshp-SWSH261</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>mgz-pkmn</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Totals:</t>
         </is>
       </c>
-      <c r="K8" s="6">
-        <f>SUM(K2:K6)</f>
+      <c r="K17" s="6">
+        <f>SUM(K2:K15)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
-        <f>SUM(L2:L6)</f>
+      <c r="L17" s="6">
+        <f>SUM(L2:L15)</f>
         <v/>
       </c>
-      <c r="M8" s="6">
-        <f>SUM(M2:M6)</f>
+      <c r="M17" s="6">
+        <f>SUM(M2:M15)</f>
         <v/>
       </c>
-      <c r="N8" s="6">
-        <f>SUM(N2:N6)</f>
+      <c r="N17" s="6">
+        <f>SUM(N2:N15)</f>
         <v/>
       </c>
-      <c r="O8" s="6">
-        <f>SUM(O2:O6)</f>
+      <c r="O17" s="6">
+        <f>SUM(O2:O15)</f>
         <v/>
       </c>
     </row>
@@ -1107,9 +1980,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
 </worksheet>
 </file>